--- a/results/05_robustness_resilience_generalizability/05_robustness_resilience_generalizability.xlsx
+++ b/results/05_robustness_resilience_generalizability/05_robustness_resilience_generalizability.xlsx
@@ -979,22 +979,22 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Baseline Control (M0)</t>
+          <t>Baseline Control</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Deterministic Baseline (M1*)</t>
+          <t>Model 1 (Deterministic)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Probabilistic (M3)</t>
+          <t>Model 2 (Machine Learning)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Dynamic Hybrid (M5)</t>
+          <t>Model 3 (Dynamic Hybrid)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>M5 Champion</t>
+          <t>Model 3 Champion</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>M5 captures 74.8% of all volatility variance on unobserved 2025 holdout.</t>
+          <t>Model 3 captures 74.8% of all volatility variance on unobserved 2025 holdout.</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>M5 Lowest Error</t>
+          <t>Model 3 Lowest Error</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>M5 slashes volatility prediction errors to 222.1 pax/hr (-91.3 pax/hr vs M1*).</t>
+          <t>Model 3 slashes volatility prediction errors to 222.1 pax/hr (-91.3 pax/hr vs Model 1).</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>M5 Lowest MAE</t>
+          <t>Model 3 Lowest MAE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>M5 achieves exceptional precision with MAE of 142.8 pax/hr across dedicated complexes.</t>
+          <t>Model 3 achieves exceptional precision with MAE of 142.8 pax/hr across dedicated complexes.</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>M5 Champion</t>
+          <t>Model 3 Champion</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M5 achieves 0.662, delivering a 33.8% error reduction over daily persistence.</t>
+          <t>Model 3 achieves 0.662, delivering a 33.8% error reduction over daily persistence.</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>M0 / M5 Minimal Bias</t>
+          <t>Baseline / Model 3 Minimal Bias</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>All models exhibit slight negative bias during peak surges; M5 exhibits -8.5 pax/hr.</t>
+          <t>All models exhibit slight negative bias during peak surges; Model 3 exhibits -8.5 pax/hr.</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>M5 Lowest RMSE</t>
+          <t>Model 3 Lowest RMSE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>M5 achieves lowest RMSE; M3 wins Routine Pareto Efficiency (low-compute, zero-feedback).</t>
+          <t>Model 3 achieves lowest RMSE; Model 2 wins Routine Pareto Efficiency (low-compute, zero-feedback).</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Target Met by M3 &amp; M5</t>
+          <t>Target Met by Model 2 &amp; Model 3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Confirms H1(a): Both M3 and M5 meet the &lt; 0.70 target under calm operations.</t>
+          <t>Confirms H1(a): Both Model 2 and Model 3 meet the &lt; 0.70 target under calm operations.</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DM Test vs. M1* Control</t>
+          <t>DM Test vs. Model 1 Control</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>M5 Lowest Shock RMSE</t>
+          <t>Model 3 Lowest Shock RMSE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>M5 minimizes absolute error during acute convective storms and ground stops.</t>
+          <t>Model 3 minimizes absolute error during acute convective storms and ground stops.</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>M5 Lowest Shock MASE</t>
+          <t>Model 3 Lowest Shock MASE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>During chaotic delay cascades M5 performs 30.6% better than naive persistence.</t>
+          <t>During chaotic delay cascades Model 3 performs 30.6% better than naive persistence.</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>M5 DECISIVE WINNER</t>
+          <t>Model 3 DECISIVE WINNER</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>M5 recursive feedback (e_{t-1}) prevents empty checkpoint collapse; M3 collapses (R=2.14).</t>
+          <t>Model 3 recursive feedback (e_{t-1}) prevents empty checkpoint collapse; Model 2 collapses (R=2.14).</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>M5 DECISIVE WINNER</t>
+          <t>Model 3 DECISIVE WINNER</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>M5 returns to normal bounds 5.0 hrs faster than M1* and 2.6 hrs faster than M3.</t>
+          <t>Model 3 returns to normal bounds 5.0 hrs faster than Model 1 and 2.6 hrs faster than Model 2.</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>M1* DECISIVE WINNER</t>
+          <t>Model 1 DECISIVE WINNER</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>M1* physical schedule rules generalize (RTR=1.04); M5 overfits to local gate layout (RTR=1.19).</t>
+          <t>Model 1 physical schedule rules generalize (RTR=1.04); Model 3 overfits to local gate layout (RTR=1.19).</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>M1* Minimal Penalty</t>
+          <t>Model 1 Minimal Penalty</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>M1* DECISIVE WINNER</t>
+          <t>Model 1 DECISIVE WINNER</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>M1* passes target (+4.0%); M5 decisively fails target (+21.5%) due to tree overfitting.</t>
+          <t>Model 1 passes target (+4.0%); Model 3 decisively fails target (+21.5%) due to tree overfitting.</t>
         </is>
       </c>
     </row>
@@ -1881,22 +1881,22 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Baseline Control (M0)</t>
+          <t>Baseline Control</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Deterministic Baseline (M1*)</t>
+          <t>Model 1 (Deterministic)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Probabilistic (M3)</t>
+          <t>Model 2 (Machine Learning)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Dynamic Hybrid (M5)</t>
+          <t>Model 3 (Dynamic Hybrid)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M5 captures 74.8% of all throughput volatility variance on unseen future data.</t>
+          <t>Model 3 captures 74.8% of all throughput volatility variance on unseen future data.</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Slashes large prediction errors by 91.3 pax/hr vs. M1*.</t>
+          <t>Slashes large prediction errors by 91.3 pax/hr vs. Model 1.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M5 achieves the academic stretch target, beating daily persistence by 33.8%.</t>
+          <t>Model 3 achieves the academic stretch target, beating daily persistence by 33.8%.</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M5 exhibits negligible bias of -8.5 pax/hr.</t>
+          <t>Model 3 exhibits negligible bias of -8.5 pax/hr.</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M5 lowest RMSE; M3 wins Routine Pareto Efficiency (low-compute, zero-feedback).</t>
+          <t>Model 3 lowest RMSE; Model 2 wins Routine Pareto Efficiency (low-compute, zero-feedback).</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Confirms H1(a): Both M3 and M5 meet target under nominal conditions.</t>
+          <t>Confirms H1(a): Both Model 2 and Model 3 meet target under nominal conditions.</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Control Baseline (M1*)</t>
+          <t>Control Baseline (Model 1)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M5 maintains tight error bounds during severe weather storms and airport ground stops.</t>
+          <t>Model 3 maintains tight error bounds during severe weather storms and airport ground stops.</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M5 performs 30.6% better than naive guessing during disruptions.</t>
+          <t>Model 3 performs 30.6% better than naive guessing during disruptions.</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M5 DECISIVE WINNER: Innovation feedback prevents empty checkpoint collapse.</t>
+          <t>Model 3 DECISIVE WINNER: Innovation feedback prevents empty checkpoint collapse.</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M5 returns to normal error bounds 5.0 hrs faster than M1* and 2.6 hrs faster than M3.</t>
+          <t>Model 3 returns to normal error bounds 5.0 hrs faster than Model 1 and 2.6 hrs faster than Model 2.</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M1* DECISIVE WINNER: Invariant schedule rules generalize; M5 overfits to local gates.</t>
+          <t>Model 1 DECISIVE WINNER: Invariant schedule rules generalize; Model 3 overfits to local gates.</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M1* passes target with +4.0% shift; M5 fails target with +21.5% shift.</t>
+          <t>Model 1 passes target with +4.0% shift; Model 3 fails target with +21.5% shift.</t>
         </is>
       </c>
     </row>
